--- a/artfynd/S 4978-2021 artfynd.xlsx
+++ b/artfynd/S 4978-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665676</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563598</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563615</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563641</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665674</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563622</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665626</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666665</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96667704</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563597</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666157</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563585</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563653</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2351,6 +2431,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666779</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2449,6 +2534,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96667796</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563595</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2671,6 +2766,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563616</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563618</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2893,6 +2998,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563640</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3004,6 +3114,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563643</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3115,6 +3230,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563654</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3226,6 +3346,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563662</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3327,6 +3452,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96667981</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3438,6 +3568,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563579</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3549,6 +3684,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563621</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3660,6 +3800,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563645</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3758,6 +3903,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665095</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3856,6 +4006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665163</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3954,6 +4109,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666689</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4065,6 +4225,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563583</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4176,6 +4341,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563584</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4287,6 +4457,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563586</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4398,6 +4573,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563588</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4509,6 +4689,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563592</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4620,6 +4805,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563601</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4731,6 +4921,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563605</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4842,6 +5037,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563611</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4953,6 +5153,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563612</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5064,6 +5269,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563628</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5175,6 +5385,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563629</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5286,6 +5501,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563632</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5397,6 +5617,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563633</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5513,6 +5738,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563657</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5624,6 +5854,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563672</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5735,6 +5970,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563673</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5846,6 +6086,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563580</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5957,6 +6202,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563625</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6068,6 +6318,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563670</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6179,6 +6434,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563578</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6290,6 +6550,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563631</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6401,6 +6666,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563639</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6512,6 +6782,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563644</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6623,6 +6898,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563655</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6734,6 +7014,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563666</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6845,6 +7130,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563668</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6956,6 +7246,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563647</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7054,6 +7349,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96663865</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7152,6 +7452,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96664174</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7250,6 +7555,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96664557</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7348,6 +7658,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96668018</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7446,6 +7761,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666200</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7544,6 +7864,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666522</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7642,6 +7967,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666959</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7740,6 +8070,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665611</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7838,6 +8173,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665628</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7936,6 +8276,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665706</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8034,6 +8379,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665728</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8137,6 +8487,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666064</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8235,6 +8590,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666126</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8333,6 +8693,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666757</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8431,6 +8796,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665612</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8529,6 +8899,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666666</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8645,6 +9020,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119499252</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8751,6 +9131,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119667203</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8853,6 +9238,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563593</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8955,6 +9345,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563626</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9054,6 +9449,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96663867</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9153,6 +9553,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96664193</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9252,6 +9657,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96664559</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9351,6 +9761,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665108</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9450,6 +9865,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665707</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9549,6 +9969,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665731</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9648,6 +10073,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96665914</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9747,6 +10177,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96666692</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9846,6 +10281,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96667770</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9947,6 +10387,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489218</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10048,6 +10493,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489220</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10159,6 +10609,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563589</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10270,6 +10725,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563590</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10381,8 +10841,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>